--- a/order_generation/PO_excel_export/factory-1.xlsx
+++ b/order_generation/PO_excel_export/factory-1.xlsx
@@ -1095,14 +1095,37 @@
       <c r="G8" s="29" t="inlineStr"/>
       <c r="H8" s="20" t="n"/>
     </row>
-    <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
+    <row r="9" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>ST1122-2</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>[图片未找到] [图片未找到]</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>透明尼龙针+猪鬃.深棕色胶皮（TPR）带纹路模具更新（7589C），0.7mm透明尼龙针+猪鬃，棕色染头（7589C）. 包装方式：散货</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F9" s="29">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>散货</t>
+        </is>
+      </c>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1141,7 +1164,11 @@
           <t>进仓地址：</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr"/>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>宁波市海曙区高桥镇秀丰路67号1栋1楼，小张，18668289261</t>
+        </is>
+      </c>
       <c r="C12" s="25" t="n"/>
       <c r="D12" s="25" t="n"/>
       <c r="E12" s="25" t="n"/>
@@ -1155,7 +1182,11 @@
           <t>付款方式:</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr"/>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>含税含运含进仓</t>
+        </is>
+      </c>
       <c r="C13" s="25" t="n"/>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="25" t="n"/>
